--- a/paiement_mensuel AOUT.xlsx
+++ b/paiement_mensuel AOUT.xlsx
@@ -518,20 +518,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -545,12 +533,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -561,11 +543,31 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -573,8 +575,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,22 +901,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="19" t="s">
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="20"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="14"/>
     </row>
     <row r="2" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
@@ -949,7 +949,7 @@
       <c r="J2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="17"/>
+      <c r="K2" s="13"/>
       <c r="L2" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,1459 +962,1465 @@
       <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="20"/>
+      <c r="Q2" s="14"/>
       <c r="R2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="22" t="s">
+      <c r="S2" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>786241266</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>301</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>240</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="6">
         <v>1.25</v>
       </c>
-      <c r="I3" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J3" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K3" s="17"/>
-      <c r="L3" s="7">
+      <c r="I3" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J3" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K3" s="13"/>
+      <c r="L3" s="5">
         <v>63</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>120</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="6">
         <v>0.52</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="5">
         <v>50000</v>
       </c>
-      <c r="P3" s="7">
+      <c r="P3" s="5">
         <v>26250</v>
       </c>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
     </row>
     <row r="4" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5"/>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>786241255</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>222</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>240</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6">
         <v>0.92</v>
       </c>
-      <c r="I4" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J4" s="7">
+      <c r="I4" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J4" s="5">
         <v>92500</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="7">
+      <c r="K4" s="13"/>
+      <c r="L4" s="5">
         <v>71</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <v>120</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="6">
         <v>0.59</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="5">
         <v>50000</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="5">
         <v>29583</v>
       </c>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
     </row>
     <row r="5" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>775812208</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>253</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>240</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="6">
         <v>1.05</v>
       </c>
-      <c r="I5" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J5" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="7">
+      <c r="I5" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J5" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K5" s="13"/>
+      <c r="L5" s="5">
         <v>44</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="5">
         <v>120</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="6">
         <v>0.37</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="5">
         <v>50000</v>
       </c>
-      <c r="P5" s="7">
+      <c r="P5" s="5">
         <v>18333</v>
       </c>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
     </row>
     <row r="6" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5"/>
-      <c r="B6" s="10" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>789160174</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>326</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>240</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>1.36</v>
       </c>
-      <c r="I6" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J6" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="7">
+      <c r="I6" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K6" s="13"/>
+      <c r="L6" s="5">
         <v>104</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>120</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="6">
         <v>0.87</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="5">
         <v>50000</v>
       </c>
-      <c r="P6" s="7">
+      <c r="P6" s="5">
         <v>43333</v>
       </c>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
     </row>
     <row r="7" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="14">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="10">
         <v>392500</v>
       </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="14">
+      <c r="K7" s="13"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="10">
         <f>SUM(P3:P6)</f>
         <v>117499</v>
       </c>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="14">
+      <c r="Q7" s="14"/>
+      <c r="R7" s="10">
         <v>150000</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="10">
         <f>SUM(J7:R7)</f>
         <v>659999</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>277</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>240</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I8" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J8" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="7">
+      <c r="I8" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J8" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="5">
         <v>110</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="5">
         <v>120</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="6">
         <v>0.92</v>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="5">
         <v>50000</v>
       </c>
-      <c r="P8" s="7">
+      <c r="P8" s="5">
         <v>45833</v>
       </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="5">
         <v>238</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>240</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <v>0.99</v>
       </c>
-      <c r="I9" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J9" s="7">
+      <c r="I9" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J9" s="5">
         <v>99167</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="7">
+      <c r="K9" s="13"/>
+      <c r="L9" s="5">
         <v>41</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="5">
         <v>120</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="6">
         <v>0.34</v>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="5">
         <v>50000</v>
       </c>
-      <c r="P9" s="7">
+      <c r="P9" s="5">
         <v>17083</v>
       </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
+      <c r="Q9" s="14"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
     </row>
     <row r="10" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>778528509</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>265</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>240</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I10" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J10" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="7">
+      <c r="I10" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="5">
         <v>136</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="5">
         <v>120</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="6">
         <v>1.1299999999999999</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="5">
         <v>50000</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="5">
         <v>50000</v>
       </c>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
+      <c r="Q10" s="14"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
     </row>
     <row r="11" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>787655222</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="5">
         <v>246</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <v>240</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>1.02</v>
       </c>
-      <c r="I11" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J11" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="7">
+      <c r="I11" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J11" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="5">
         <v>74</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="5">
         <v>120</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="6">
         <v>0.62</v>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="5">
         <v>50000</v>
       </c>
-      <c r="P11" s="7">
+      <c r="P11" s="5">
         <v>30833</v>
       </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
+      <c r="Q11" s="14"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
     </row>
     <row r="12" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14">
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="10">
         <v>399167</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="14">
+      <c r="K12" s="13"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="10">
         <f>SUM(P8:P11)</f>
         <v>143749</v>
       </c>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="14">
+      <c r="Q12" s="14"/>
+      <c r="R12" s="10">
         <v>150000</v>
       </c>
-      <c r="S12" s="14">
+      <c r="S12" s="10">
         <f>+SUM(J12:R12)</f>
         <v>692916</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="5">
         <v>236</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <v>240</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="6">
         <v>0.98</v>
       </c>
-      <c r="I13" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J13" s="7">
+      <c r="I13" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J13" s="5">
         <v>98333</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="7">
+      <c r="K13" s="13"/>
+      <c r="L13" s="5">
         <v>29</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="5">
         <v>120</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="6">
         <v>0.24</v>
       </c>
-      <c r="O13" s="7">
+      <c r="O13" s="5">
         <v>50000</v>
       </c>
-      <c r="P13" s="7">
+      <c r="P13" s="5">
         <v>12083</v>
       </c>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
     </row>
     <row r="14" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7">
+      <c r="E14" s="5"/>
+      <c r="F14" s="5">
         <v>247</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <v>240</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="6">
         <v>1.03</v>
       </c>
-      <c r="I14" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J14" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="7">
+      <c r="I14" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="5">
         <v>20</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="5">
         <v>120</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="6">
         <v>0.17</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="5">
         <v>50000</v>
       </c>
-      <c r="P14" s="7">
+      <c r="P14" s="5">
         <v>8333</v>
       </c>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
     </row>
     <row r="15" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="5">
         <v>235</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <v>240</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="6">
         <v>0.98</v>
       </c>
-      <c r="I15" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J15" s="7">
+      <c r="I15" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J15" s="5">
         <v>97917</v>
       </c>
-      <c r="K15" s="17"/>
-      <c r="L15" s="7">
+      <c r="K15" s="13"/>
+      <c r="L15" s="5">
         <v>69</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="5">
         <v>120</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="6">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="5">
         <v>50000</v>
       </c>
-      <c r="P15" s="7">
+      <c r="P15" s="5">
         <v>28750</v>
       </c>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
     </row>
     <row r="16" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="5">
         <v>182</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <v>240</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <v>0.76</v>
       </c>
-      <c r="I16" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="I16" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J16" s="5">
         <v>75833</v>
       </c>
-      <c r="K16" s="17"/>
-      <c r="L16" s="7">
+      <c r="K16" s="13"/>
+      <c r="L16" s="5">
         <v>14</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="5">
         <v>120</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="6">
         <v>0.12</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="5">
         <v>50000</v>
       </c>
-      <c r="P16" s="7">
+      <c r="P16" s="5">
         <v>5833</v>
       </c>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
     </row>
     <row r="17" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14">
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="10">
         <v>372083</v>
       </c>
-      <c r="K17" s="17"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="14">
+      <c r="K17" s="13"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="10">
         <f>SUM(P13:P16)</f>
         <v>54999</v>
       </c>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="14">
+      <c r="Q17" s="14"/>
+      <c r="R17" s="10">
         <v>150000</v>
       </c>
-      <c r="S17" s="14">
+      <c r="S17" s="10">
         <f>+SUM(J17:R17)</f>
         <v>577082</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>775810336</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="5">
         <v>198</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <v>240</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <v>0.82</v>
       </c>
-      <c r="I18" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J18" s="7">
+      <c r="I18" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J18" s="5">
         <v>82500</v>
       </c>
-      <c r="K18" s="17"/>
-      <c r="L18" s="7">
+      <c r="K18" s="13"/>
+      <c r="L18" s="5">
         <v>0</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="5">
         <v>120</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="6">
         <v>0</v>
       </c>
-      <c r="O18" s="7">
+      <c r="O18" s="5">
         <v>50000</v>
       </c>
-      <c r="P18" s="7">
+      <c r="P18" s="5">
         <v>0</v>
       </c>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
     </row>
     <row r="19" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>778525987</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="5">
         <v>201</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="5">
         <v>240</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>0.84</v>
       </c>
-      <c r="I19" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J19" s="7">
+      <c r="I19" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J19" s="5">
         <v>83750</v>
       </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="7">
+      <c r="K19" s="13"/>
+      <c r="L19" s="5">
         <v>4</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="5">
         <v>120</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="6">
         <v>0.03</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="5">
         <v>50000</v>
       </c>
-      <c r="P19" s="7">
+      <c r="P19" s="5">
         <v>1667</v>
       </c>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
     </row>
     <row r="20" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>772104981</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="5">
         <v>274</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="5">
         <v>240</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="6">
         <v>1.1399999999999999</v>
       </c>
-      <c r="I20" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J20" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K20" s="17"/>
-      <c r="L20" s="7">
+      <c r="I20" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J20" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="5">
         <v>1</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="5">
         <v>120</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="6">
         <v>0.01</v>
       </c>
-      <c r="O20" s="7">
+      <c r="O20" s="5">
         <v>50000</v>
       </c>
-      <c r="P20" s="7">
+      <c r="P20" s="5">
         <v>417</v>
       </c>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
     </row>
     <row r="21" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>772107591</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="5">
         <v>297</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="5">
         <v>240</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="6">
         <v>1.24</v>
       </c>
-      <c r="I21" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J21" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K21" s="17"/>
-      <c r="L21" s="7">
+      <c r="I21" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J21" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K21" s="13"/>
+      <c r="L21" s="5">
         <v>2</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="5">
         <v>120</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="6">
         <v>0.02</v>
       </c>
-      <c r="O21" s="7">
+      <c r="O21" s="5">
         <v>50000</v>
       </c>
-      <c r="P21" s="7">
+      <c r="P21" s="5">
         <v>833</v>
       </c>
-      <c r="Q21" s="20"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
     </row>
     <row r="22" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="14">
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="10">
         <v>366250</v>
       </c>
-      <c r="K22" s="17"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="14">
+      <c r="K22" s="13"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="10">
         <f>SUM(P18:P21)</f>
         <v>2917</v>
       </c>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="14">
+      <c r="Q22" s="14"/>
+      <c r="R22" s="10">
         <v>150000</v>
       </c>
-      <c r="S22" s="14">
+      <c r="S22" s="10">
         <f>+SUM(J22:R22)</f>
         <v>519167</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>782989910</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="5">
         <v>303</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="5">
         <v>240</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="6">
         <v>1.26</v>
       </c>
-      <c r="I23" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J23" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K23" s="17"/>
-      <c r="L23" s="7">
+      <c r="I23" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J23" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K23" s="13"/>
+      <c r="L23" s="5">
         <v>93</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M23" s="5">
         <v>120</v>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="6">
         <v>0.78</v>
       </c>
-      <c r="O23" s="7">
+      <c r="O23" s="5">
         <v>50000</v>
       </c>
-      <c r="P23" s="7">
+      <c r="P23" s="5">
         <v>38750</v>
       </c>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
     </row>
     <row r="24" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>787095594</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="5">
         <v>285</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="5">
         <v>240</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="6">
         <v>1.19</v>
       </c>
-      <c r="I24" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J24" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K24" s="17"/>
-      <c r="L24" s="7">
+      <c r="I24" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K24" s="13"/>
+      <c r="L24" s="5">
         <v>26</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="5">
         <v>120</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="6">
         <v>0.22</v>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="5">
         <v>50000</v>
       </c>
-      <c r="P24" s="7">
+      <c r="P24" s="5">
         <v>10833</v>
       </c>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
     </row>
     <row r="25" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>781180981</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="5">
         <v>302</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="5">
         <v>240</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <v>1.26</v>
       </c>
-      <c r="I25" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J25" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K25" s="17"/>
-      <c r="L25" s="7">
+      <c r="I25" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J25" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K25" s="13"/>
+      <c r="L25" s="5">
         <v>13</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="5">
         <v>120</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="6">
         <v>0.11</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="5">
         <v>50000</v>
       </c>
-      <c r="P25" s="7">
+      <c r="P25" s="5">
         <v>5417</v>
       </c>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
     </row>
     <row r="26" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>787095584</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="5">
         <v>267</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="5">
         <v>240</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="6">
         <v>1.1100000000000001</v>
       </c>
-      <c r="I26" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J26" s="7">
-        <v>100000</v>
-      </c>
-      <c r="K26" s="17"/>
-      <c r="L26" s="7">
+      <c r="I26" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>100000</v>
+      </c>
+      <c r="K26" s="13"/>
+      <c r="L26" s="5">
         <v>3</v>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="5">
         <v>120</v>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="6">
         <v>0.02</v>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="5">
         <v>50000</v>
       </c>
-      <c r="P26" s="7">
+      <c r="P26" s="5">
         <v>1250</v>
       </c>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
     </row>
     <row r="27" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="14">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="10">
         <v>400000</v>
       </c>
-      <c r="K27" s="17"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="14">
+      <c r="K27" s="13"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="10">
         <f>SUM(P23:P26)</f>
         <v>56250</v>
       </c>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="14">
+      <c r="Q27" s="14"/>
+      <c r="R27" s="10">
         <v>150000</v>
       </c>
-      <c r="S27" s="14">
+      <c r="S27" s="10">
         <f>+SUM(J27:R27)</f>
         <v>606250</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="5">
         <v>192</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="5">
         <v>240</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="6">
         <v>0.8</v>
       </c>
-      <c r="I28" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J28" s="7">
+      <c r="I28" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J28" s="5">
         <v>80000</v>
       </c>
-      <c r="K28" s="17"/>
-      <c r="L28" s="7">
+      <c r="K28" s="13"/>
+      <c r="L28" s="5">
         <v>3</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="5">
         <v>120</v>
       </c>
-      <c r="N28" s="8">
+      <c r="N28" s="6">
         <v>0.02</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="5">
         <v>50000</v>
       </c>
-      <c r="P28" s="7">
+      <c r="P28" s="5">
         <v>1250</v>
       </c>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
     </row>
     <row r="29" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="5">
         <v>160</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="5">
         <v>240</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="6">
         <v>0.67</v>
       </c>
-      <c r="I29" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J29" s="7">
+      <c r="I29" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J29" s="5">
         <v>66667</v>
       </c>
-      <c r="K29" s="17"/>
-      <c r="L29" s="7">
+      <c r="K29" s="13"/>
+      <c r="L29" s="5">
         <v>1</v>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="5">
         <v>120</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="6">
         <v>0.01</v>
       </c>
-      <c r="O29" s="7">
+      <c r="O29" s="5">
         <v>50000</v>
       </c>
-      <c r="P29" s="7">
+      <c r="P29" s="5">
         <v>417</v>
       </c>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
     </row>
     <row r="30" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="5">
         <v>106</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="5">
         <v>240</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="6">
         <v>0.44</v>
       </c>
-      <c r="I30" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J30" s="7">
+      <c r="I30" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J30" s="5">
         <v>44167</v>
       </c>
-      <c r="K30" s="17"/>
-      <c r="L30" s="7">
+      <c r="K30" s="13"/>
+      <c r="L30" s="5">
         <v>0</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="5">
         <v>120</v>
       </c>
-      <c r="N30" s="8">
+      <c r="N30" s="6">
         <v>0</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="5">
         <v>50000</v>
       </c>
-      <c r="P30" s="7">
+      <c r="P30" s="5">
         <v>0</v>
       </c>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
     </row>
     <row r="31" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7">
+      <c r="E31" s="5"/>
+      <c r="F31" s="5">
         <v>191</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="5">
         <v>240</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="6">
         <v>0.8</v>
       </c>
-      <c r="I31" s="7">
-        <v>100000</v>
-      </c>
-      <c r="J31" s="7">
+      <c r="I31" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J31" s="5">
         <v>79583</v>
       </c>
-      <c r="K31" s="17"/>
-      <c r="L31" s="7">
+      <c r="K31" s="13"/>
+      <c r="L31" s="5">
         <v>2</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="5">
         <v>120</v>
       </c>
-      <c r="N31" s="8">
+      <c r="N31" s="6">
         <v>0.02</v>
       </c>
-      <c r="O31" s="7">
+      <c r="O31" s="5">
         <v>50000</v>
       </c>
-      <c r="P31" s="7">
+      <c r="P31" s="5">
         <v>833</v>
       </c>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
     </row>
     <row r="32" spans="1:19" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="14">
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="10">
         <v>270417</v>
       </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="14">
+      <c r="K32" s="13"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="10">
         <f>SUM(P28:P31)</f>
         <v>2500</v>
       </c>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="14">
+      <c r="Q32" s="14"/>
+      <c r="R32" s="10">
         <v>150000</v>
       </c>
-      <c r="S32" s="14">
+      <c r="S32" s="10">
         <f>+SUM(J32:R32)</f>
         <v>422917</v>
       </c>
     </row>
     <row r="33" spans="11:19" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="K33" s="17"/>
-      <c r="L33" s="24" t="s">
+      <c r="K33" s="13"/>
+      <c r="L33" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="24">
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="21">
         <f>+SUM(S7:S32)</f>
         <v>3478331</v>
       </c>
-      <c r="S33" s="24"/>
+      <c r="S33" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A23:A26"/>
     <mergeCell ref="L33:P33"/>
     <mergeCell ref="R33:S33"/>
     <mergeCell ref="F1:J1"/>
@@ -2425,12 +2431,6 @@
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B23:B26"/>
     <mergeCell ref="B28:B31"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A28:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2470,151 +2470,151 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="11">
         <v>775499999</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="12">
         <v>655999</v>
       </c>
-      <c r="E2" s="28">
-        <f>+D2*0.05</f>
+      <c r="E2" s="19">
+        <f t="shared" ref="E2:E7" si="0">+D2*0.05</f>
         <v>32799.950000000004</v>
       </c>
-      <c r="F2" s="28">
-        <f>SUM(D2:E2)</f>
+      <c r="F2" s="19">
+        <f t="shared" ref="F2:F7" si="1">SUM(D2:E2)</f>
         <v>688798.95</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <v>776247047</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="12">
         <v>692916</v>
       </c>
-      <c r="E3" s="28">
-        <f>+D3*0.05</f>
+      <c r="E3" s="19">
+        <f t="shared" si="0"/>
         <v>34645.800000000003</v>
       </c>
-      <c r="F3" s="28">
-        <f>SUM(D3:E3)</f>
+      <c r="F3" s="19">
+        <f t="shared" si="1"/>
         <v>727561.8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>775499999</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="12">
         <v>577082</v>
       </c>
-      <c r="E4" s="28">
-        <f>+D4*0.05</f>
+      <c r="E4" s="19">
+        <f t="shared" si="0"/>
         <v>28854.100000000002</v>
       </c>
-      <c r="F4" s="28">
-        <f>SUM(D4:E4)</f>
+      <c r="F4" s="19">
+        <f t="shared" si="1"/>
         <v>605936.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>773316647</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="12">
         <v>519167</v>
       </c>
-      <c r="E5" s="28">
-        <f>+D5*0.05</f>
+      <c r="E5" s="19">
+        <f t="shared" si="0"/>
         <v>25958.350000000002</v>
       </c>
-      <c r="F5" s="28">
-        <f>SUM(D5:E5)</f>
+      <c r="F5" s="19">
+        <f t="shared" si="1"/>
         <v>545125.35</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>774981290</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="12">
         <v>606250</v>
       </c>
-      <c r="E6" s="28">
-        <f>+D6*0.05</f>
+      <c r="E6" s="19">
+        <f t="shared" si="0"/>
         <v>30312.5</v>
       </c>
-      <c r="F6" s="28">
-        <f>SUM(D6:E6)</f>
+      <c r="F6" s="19">
+        <f t="shared" si="1"/>
         <v>636562.5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>774317541</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="12">
         <v>422917</v>
       </c>
-      <c r="E7" s="28">
-        <f>+D7*0.05</f>
+      <c r="E7" s="19">
+        <f t="shared" si="0"/>
         <v>21145.850000000002</v>
       </c>
-      <c r="F7" s="28">
-        <f>SUM(D7:E7)</f>
+      <c r="F7" s="19">
+        <f t="shared" si="1"/>
         <v>444062.85</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="14">
+      <c r="C8" s="29"/>
+      <c r="D8" s="10">
         <f>SUM(D2:D7)</f>
         <v>3474331</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="20">
         <f>SUM(E2:E7)</f>
         <v>173716.55000000002</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="20">
         <f>SUM(F2:F7)</f>
         <v>3648047.5500000003</v>
       </c>
